--- a/predictions/20260913/騎手運勢2026.09.12.xlsx
+++ b/predictions/20260913/騎手運勢2026.09.12.xlsx
@@ -6,7 +6,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="2026.09.12" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="2026.09.12" sheetId="34" state="visible" r:id="rId36"/>
     <sheet name="2026.08.22" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="2026.08.15" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="2026.06.06.7 (2)" sheetId="3" state="visible" r:id="rId3"/>
